--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_1/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_1/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.7073</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7941</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5684</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2857</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8227</v>
       </c>
     </row>
@@ -1199,7 +1213,6 @@
       <c r="D2" t="n">
         <v>0.7534</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1220,7 +1233,6 @@
           <t>['AU_23', 'AU_24']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_58</t>
@@ -1231,7 +1243,6 @@
           <t>leader, portal</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1250,7 +1261,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1301,14 +1311,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Contract Layer (DTO/Mappers)</t>
@@ -1333,13 +1340,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU20</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1380,14 +1385,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1414,13 +1416,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1461,14 +1461,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1494,13 +1491,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1541,14 +1536,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1577,13 +1569,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,14 +1614,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1660,13 +1647,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1707,14 +1692,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1739,13 +1721,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1766,7 +1746,6 @@
       <c r="D9" t="n">
         <v>0.892</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1787,7 +1766,6 @@
           <t>['AU_30', 'AU_31']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_61</t>
@@ -1798,7 +1776,6 @@
           <t>angular, spring boot</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1817,7 +1794,6 @@
           <t>CF_M05_AU06, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU24</t>
@@ -1868,14 +1844,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -1901,13 +1874,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1948,14 +1919,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -1979,13 +1947,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2026,14 +1992,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2058,13 +2021,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2105,14 +2066,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2136,13 +2094,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2183,14 +2139,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_47</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -2217,13 +2170,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2264,7 +2215,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2275,7 +2225,6 @@
           <t>P_05</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2297,14 +2246,11 @@
       <c r="P15" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2345,14 +2291,11 @@
           <t>84</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_53</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>SonarQube</t>
@@ -2379,13 +2322,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2426,7 +2367,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2437,7 +2377,6 @@
           <t>P_02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
@@ -2457,14 +2396,11 @@
       <c r="P17" t="n">
         <v>60</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2505,14 +2441,11 @@
           <t>62</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>View</t>
@@ -2538,13 +2471,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2585,14 +2516,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_29</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>GSB</t>
@@ -2617,13 +2545,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2669,13 +2595,11 @@
           <t>['AU_64']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_32</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2700,13 +2624,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2747,14 +2669,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_48</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2778,13 +2697,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU33</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2825,14 +2742,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Ordering</t>
@@ -2859,13 +2773,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_AU11</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2906,14 +2818,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_46</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
@@ -2939,13 +2848,11 @@
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2986,14 +2893,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -3019,13 +2923,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3066,7 +2968,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3077,7 +2978,6 @@
           <t>P_04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -3097,14 +2997,11 @@
       <c r="P25" t="n">
         <v>62</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3145,14 +3042,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -3176,13 +3070,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3223,14 +3115,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Model</t>
@@ -3256,13 +3145,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3303,7 +3190,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3314,7 +3200,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3335,7 +3220,6 @@
       <c r="P28" t="n">
         <v>61</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3346,7 +3230,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3387,14 +3270,11 @@
           <t>64</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>ViewModel</t>
@@ -3420,13 +3300,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3467,14 +3345,11 @@
           <t>87</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_55</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Grafana</t>
@@ -3498,13 +3373,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M05_AU09</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3578,7 +3451,6 @@
           <t>Volkswagen Group Services</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Volkswagen Group Services forms part of Volkswagen Group, a German multinational automotive manufacturing group and one of the world's largest automobile manufacturers, and exists to exclusively support the different group companies on a worldwide scale.</t>
@@ -3614,7 +3486,6 @@
           <t>Integration Bus</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>A software infrastructure that allows communication and data exchange between different applications or services within the same computer environment.</t>
@@ -3650,7 +3521,6 @@
           <t>Cloud Services Layer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>A cloud-based service layer that provides solutions and applications directed to the group's importers according to business needs.</t>
@@ -3686,7 +3556,6 @@
           <t>NADIN</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>A program that manages a global change in the architecture of all applications within its market.</t>
@@ -3722,7 +3591,6 @@
           <t>NiX UK</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>An integration bus solution developed in Spain as a cloud-based service layer.</t>
@@ -3758,7 +3626,6 @@
           <t>NiX MED</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>A very similar solution for the Mediterranean market developed in parallel.</t>
@@ -3794,7 +3661,6 @@
           <t>Business Area</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The main public of the application is the business area in charge of commercial activities related to product importation.</t>
@@ -3830,7 +3696,6 @@
           <t>Business Support Area</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>This area helps the previous one with daily tasks like configuring addresses or parameters.</t>
@@ -3866,7 +3731,6 @@
           <t>After Sales Support (AMS)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The new application will improve daily process monitoring and problem resolution, reducing the probability of manual errors.</t>
@@ -3902,7 +3766,6 @@
           <t>Controller</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Inside each microservice there is a Controller class for each model.</t>
@@ -3938,7 +3801,6 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Services offer the interface and implementation of all the business logic of the application.</t>
@@ -3974,7 +3836,6 @@
           <t>DTO</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow structuring the data necessary for each request, providing a customized format depending on response requirements.</t>
@@ -4010,7 +3871,6 @@
           <t>Mapper</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Mappers are responsible for conversion between DTOs and models.</t>
@@ -4046,7 +3906,6 @@
           <t>Repository</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Repositories are in charge of executing queries on the database.</t>
@@ -4082,7 +3941,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>The data format employed is JSON.</t>
@@ -4118,7 +3976,6 @@
           <t>Angular CLI</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>The construction and execution of all the frontEnd is carried out employing Angular CLI which generates an optimized and minimized version of the application.</t>
@@ -4154,7 +4011,6 @@
           <t>Angular 11+</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Angular is a web development framework created by Google, based on the JavaScript superset programming language called TypeScript, that allows building modern single-page web applications (SPA).</t>
@@ -4190,7 +4046,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>TypeScript superset programming language of JavaScript.</t>
@@ -4226,7 +4081,6 @@
           <t>Spring Data &amp; JPA 2.2</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Spring Data is a Spring project that simplifies data access and management in Java applications, while JPA (Java Persistence API) is a specification that defines how to map Java objects to relational databases.</t>
@@ -4262,7 +4116,6 @@
           <t>Spring</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Spring framework for Java applications.</t>
@@ -4298,7 +4151,6 @@
           <t>JPA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Java Persistence API.</t>
@@ -4334,7 +4186,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Java language that we will use throughout the project.</t>
@@ -4370,7 +4221,6 @@
           <t>Spring Boot 2.2.2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Spring Boot is a framework that simplifies the creation of Spring-based Java applications, offering automatic configuration and tools that allow deploying applications quickly.</t>
@@ -4406,7 +4256,6 @@
           <t>Java OpenJDK 17</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>OpenJDK is a free and open implementation of the Java Development Kit (JDK), the platform to develop and execute Java applications.</t>
@@ -4442,7 +4291,6 @@
           <t>Gitflow</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Gitflow methodology defines a clear set of branches with specific purposes and a workflow to manage development, tests, and release of the application.</t>
@@ -4478,7 +4326,6 @@
           <t>IntelliJ IDEA</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>IntelliJ IDEA is an integrated development environment (IDE) created by JetBrains, designed primarily for software development in Java.</t>
@@ -4514,7 +4361,6 @@
           <t>Visual Studio Code</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Visual Studio Code is a lightweight, cross-platform, and free source code editor developed by Microsoft.</t>
@@ -4550,7 +4396,6 @@
           <t>Amazon ECR</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>These images are stored in Amazon ECR (Elastic Container Registry).</t>
@@ -4586,7 +4431,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Amazon Web Services is a consolidated cloud platform with robust services and a reliable infrastructure.</t>
@@ -4622,7 +4466,6 @@
           <t>JUnit 5</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>For unit tests, JUnit 5 and Mockito libraries have been used.</t>
@@ -4658,7 +4501,6 @@
           <t>Mockito</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Mockito is a mocks (simulations) library which allows testing a class without depending on other real components.</t>
@@ -4694,7 +4536,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>For this task, Postman application has been used to be able to test the modified calls given that there are no screens of the Ordering microservice in the application.</t>
@@ -4730,7 +4571,6 @@
           <t>Spring Boot Actuator</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Spring Boot has native support to expose metrics and information of the application state through the Spring Boot Actuator module.</t>
@@ -4761,7 +4601,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>cloud services layer, nix uk</t>
@@ -4797,7 +4636,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>portal, access control</t>
@@ -4833,7 +4671,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>access control, repository</t>
@@ -4869,7 +4706,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>view, viewmodel</t>
@@ -4905,7 +4741,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>controller, service</t>
@@ -4941,7 +4776,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>angular, spring boot</t>
@@ -4982,7 +4816,6 @@
           <t>Microservices Architecture</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Consists of dividing the system into a set of small, independent and autonomous services where each microservice takes care of a specific functionality and communicates with the rest by means of diverse messaging systems.</t>
@@ -5074,7 +4907,6 @@
           <t>Client (Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -5112,7 +4944,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -5149,7 +4980,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -5182,7 +5012,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client (frontend), amazon eks</t>
@@ -5218,7 +5047,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -5254,7 +5082,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -5290,7 +5117,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -5331,7 +5157,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -5368,7 +5193,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -5400,7 +5224,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>viewmodel, server (backend)</t>
@@ -5441,7 +5264,6 @@
           <t>Microservices</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Application has an architecture based on microservices.</t>
@@ -5477,7 +5299,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -5490,7 +5311,6 @@
           <t>AU_60</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0.7669</v>
       </c>
